--- a/public/converted/ceny-dlya-nakladnoy-ot-bah-30-10-26.xlsx
+++ b/public/converted/ceny-dlya-nakladnoy-ot-bah-30-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$1:$D$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$1:$G$338</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -51,16 +53,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,13 +430,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:G339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,6 +463,21 @@
           <t>Сумма</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Вес 1 шт, кг</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вес строки, кг</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Откуда вес</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,6 +494,17 @@
       <c r="D2" s="3" t="n">
         <v>3699</v>
       </c>
+      <c r="E2" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M1721 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,6 +521,17 @@
       <c r="D3" s="3" t="n">
         <v>8048.25</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-M216S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -504,6 +548,17 @@
       <c r="D4" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -520,6 +575,17 @@
       <c r="D5" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,6 +602,17 @@
       <c r="D6" s="3" t="n">
         <v>56238.75</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -552,6 +629,17 @@
       <c r="D7" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -568,6 +656,17 @@
       <c r="D8" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-G210S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -584,6 +683,17 @@
       <c r="D9" s="3" t="n">
         <v>674.75</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -600,6 +710,17 @@
       <c r="D10" s="3" t="n">
         <v>699.75</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M179 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -616,6 +737,17 @@
       <c r="D11" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -632,6 +764,17 @@
       <c r="D12" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -648,6 +791,17 @@
       <c r="D13" s="3" t="n">
         <v>3748.75</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M158 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -664,6 +818,17 @@
       <c r="D14" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M1561 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -680,6 +845,17 @@
       <c r="D15" s="3" t="n">
         <v>4998.75</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -696,6 +872,17 @@
       <c r="D16" s="3" t="n">
         <v>1399.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M1552 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -712,6 +899,17 @@
       <c r="D17" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M1301D б/у</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -728,6 +926,17 @@
       <c r="D18" s="3" t="n">
         <v>11997</v>
       </c>
+      <c r="E18" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-G200S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -744,6 +953,17 @@
       <c r="D19" s="3" t="n">
         <v>23393.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -760,6 +980,17 @@
       <c r="D20" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-G191 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -776,6 +1007,17 @@
       <c r="D21" s="3" t="n">
         <v>7647.75</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-G185 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -792,6 +1034,17 @@
       <c r="D22" s="3" t="n">
         <v>3249.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -808,6 +1061,17 @@
       <c r="D23" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E23" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -824,6 +1088,17 @@
       <c r="D24" s="3" t="n">
         <v>17548.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>4.451</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>26.706</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «хлебопечь» все бренды — 88 шт</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -840,6 +1115,17 @@
       <c r="D25" s="3" t="n">
         <v>14373.75</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>4.451</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>22.255</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «хлебопечь» все бренды — 88 шт</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -856,6 +1142,17 @@
       <c r="D26" s="3" t="n">
         <v>6499.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>4.451</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>8.901999999999999</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «хлебопечь» все бренды — 88 шт</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -872,6 +1169,17 @@
       <c r="D27" s="3" t="n">
         <v>36746.25</v>
       </c>
+      <c r="E27" s="4" t="n">
+        <v>4.451</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>66.765</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «хлебопечь» все бренды — 88 шт</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -888,6 +1196,17 @@
       <c r="D28" s="3" t="n">
         <v>1499.25</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «фен» Redmond/Red — 3 шт</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -904,6 +1223,17 @@
       <c r="D29" s="3" t="n">
         <v>1749.75</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «фен» Redmond/Red — 3 шт</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -920,6 +1250,17 @@
       <c r="D30" s="3" t="n">
         <v>1424.75</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -936,6 +1277,17 @@
       <c r="D31" s="3" t="n">
         <v>4998.75</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -952,6 +1304,17 @@
       <c r="D32" s="3" t="n">
         <v>10447.25</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -968,6 +1331,17 @@
       <c r="D33" s="3" t="n">
         <v>774.75</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -984,6 +1358,17 @@
       <c r="D34" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1000,6 +1385,17 @@
       <c r="D35" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1016,6 +1412,17 @@
       <c r="D36" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1032,6 +1439,17 @@
       <c r="D37" s="3" t="n">
         <v>2249.25</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1048,6 +1466,17 @@
       <c r="D38" s="3" t="n">
         <v>674.75</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1064,6 +1493,17 @@
       <c r="D39" s="3" t="n">
         <v>11247.75</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1080,6 +1520,17 @@
       <c r="D40" s="3" t="n">
         <v>4623.75</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1096,6 +1547,17 @@
       <c r="D41" s="3" t="n">
         <v>3499</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1112,6 +1574,17 @@
       <c r="D42" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1128,6 +1601,17 @@
       <c r="D43" s="3" t="n">
         <v>3999</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1144,6 +1628,17 @@
       <c r="D44" s="3" t="n">
         <v>799.75</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1160,6 +1655,17 @@
       <c r="D45" s="3" t="n">
         <v>3749.25</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1176,6 +1682,17 @@
       <c r="D46" s="3" t="n">
         <v>799.75</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1192,6 +1709,13 @@
       <c r="D47" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1208,6 +1732,13 @@
       <c r="D48" s="3" t="n">
         <v>5999.25</v>
       </c>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1224,6 +1755,13 @@
       <c r="D49" s="3" t="n">
         <v>15122.25</v>
       </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1240,6 +1778,17 @@
       <c r="D50" s="3" t="n">
         <v>4124.75</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «духовой шкаф» все бренды — 5 шт</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1256,6 +1805,17 @@
       <c r="D51" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «увлажнитель» все бренды — 656 шт</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1272,6 +1832,17 @@
       <c r="D52" s="3" t="n">
         <v>2548.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «тостер» все бренды — 493 шт</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1288,6 +1859,17 @@
       <c r="D53" s="3" t="n">
         <v>849.75</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «тостер» все бренды — 493 шт</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1304,6 +1886,17 @@
       <c r="D54" s="3" t="n">
         <v>7999</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1320,6 +1913,17 @@
       <c r="D55" s="3" t="n">
         <v>16497.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1336,6 +1940,13 @@
       <c r="D56" s="3" t="n">
         <v>449.75</v>
       </c>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1352,6 +1963,13 @@
       <c r="D57" s="3" t="n">
         <v>1949.25</v>
       </c>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1368,6 +1986,17 @@
       <c r="D58" s="3" t="n">
         <v>4499.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1384,6 +2013,17 @@
       <c r="D59" s="3" t="n">
         <v>5999.25</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1400,6 +2040,17 @@
       <c r="D60" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1416,6 +2067,17 @@
       <c r="D61" s="3" t="n">
         <v>2724.75</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1432,6 +2094,13 @@
       <c r="D62" s="3" t="n">
         <v>9749.25</v>
       </c>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1448,6 +2117,13 @@
       <c r="D63" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1464,6 +2140,17 @@
       <c r="D64" s="3" t="n">
         <v>3999.75</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1480,6 +2167,17 @@
       <c r="D65" s="3" t="n">
         <v>14998.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1496,6 +2194,17 @@
       <c r="D66" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1512,6 +2221,17 @@
       <c r="D67" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1528,6 +2248,17 @@
       <c r="D68" s="3" t="n">
         <v>16873.75</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1544,6 +2275,17 @@
       <c r="D69" s="3" t="n">
         <v>39372.75</v>
       </c>
+      <c r="E69" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1560,6 +2302,17 @@
       <c r="D70" s="3" t="n">
         <v>139993</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1576,6 +2329,17 @@
       <c r="D71" s="3" t="n">
         <v>16498.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1592,6 +2356,17 @@
       <c r="D72" s="3" t="n">
         <v>93750</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1608,6 +2383,17 @@
       <c r="D73" s="3" t="n">
         <v>42747.75</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1624,6 +2410,17 @@
       <c r="D74" s="3" t="n">
         <v>3749.75</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1640,6 +2437,17 @@
       <c r="D75" s="3" t="n">
         <v>22492.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1656,6 +2464,17 @@
       <c r="D76" s="3" t="n">
         <v>125196</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1672,6 +2491,17 @@
       <c r="D77" s="3" t="n">
         <v>1749.75</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1688,6 +2518,17 @@
       <c r="D78" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E78" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1704,6 +2545,17 @@
       <c r="D79" s="3" t="n">
         <v>1749.75</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1720,6 +2572,17 @@
       <c r="D80" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1736,6 +2599,17 @@
       <c r="D81" s="3" t="n">
         <v>9998.75</v>
       </c>
+      <c r="E81" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1752,6 +2626,17 @@
       <c r="D82" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1768,6 +2653,17 @@
       <c r="D83" s="3" t="n">
         <v>1649.75</v>
       </c>
+      <c r="E83" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1784,6 +2680,17 @@
       <c r="D84" s="3" t="n">
         <v>11499</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1800,6 +2707,13 @@
       <c r="D85" s="3" t="n">
         <v>524.75</v>
       </c>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1816,6 +2730,17 @@
       <c r="D86" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E86" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «плита» все бренды — 173 шт</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1832,6 +2757,17 @@
       <c r="D87" s="3" t="n">
         <v>22349.25</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1848,6 +2784,17 @@
       <c r="D88" s="3" t="n">
         <v>13498.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1864,6 +2811,17 @@
       <c r="D89" s="3" t="n">
         <v>5499.75</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1880,6 +2838,17 @@
       <c r="D90" s="3" t="n">
         <v>8999.5</v>
       </c>
+      <c r="E90" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>5.166</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «парогенератор» все бренды — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1896,6 +2865,17 @@
       <c r="D91" s="3" t="n">
         <v>4499.75</v>
       </c>
+      <c r="E91" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «парогенератор» все бренды — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1912,6 +2892,17 @@
       <c r="D92" s="3" t="n">
         <v>3748.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1928,6 +2919,17 @@
       <c r="D93" s="3" t="n">
         <v>22995</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1944,6 +2946,17 @@
       <c r="D94" s="3" t="n">
         <v>2499.5</v>
       </c>
+      <c r="E94" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1960,6 +2973,17 @@
       <c r="D95" s="3" t="n">
         <v>3749.25</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1976,6 +3000,17 @@
       <c r="D96" s="3" t="n">
         <v>4124.25</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1992,6 +3027,17 @@
       <c r="D97" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E97" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2008,6 +3054,17 @@
       <c r="D98" s="3" t="n">
         <v>24747.25</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2024,6 +3081,17 @@
       <c r="D99" s="3" t="n">
         <v>5499.5</v>
       </c>
+      <c r="E99" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2040,6 +3108,17 @@
       <c r="D100" s="3" t="n">
         <v>2499.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2056,6 +3135,17 @@
       <c r="D101" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2072,6 +3162,17 @@
       <c r="D102" s="3" t="n">
         <v>4299.5</v>
       </c>
+      <c r="E102" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2088,6 +3189,17 @@
       <c r="D103" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E103" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2104,6 +3216,17 @@
       <c r="D104" s="3" t="n">
         <v>25297.25</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2120,6 +3243,17 @@
       <c r="D105" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2136,6 +3270,17 @@
       <c r="D106" s="3" t="n">
         <v>12749.25</v>
       </c>
+      <c r="E106" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2152,6 +3297,13 @@
       <c r="D107" s="3" t="n">
         <v>4874.25</v>
       </c>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2168,6 +3320,13 @@
       <c r="D108" s="3" t="n">
         <v>2249.25</v>
       </c>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2184,6 +3343,13 @@
       <c r="D109" s="3" t="n">
         <v>874.75</v>
       </c>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2200,6 +3366,13 @@
       <c r="D110" s="3" t="n">
         <v>4499.25</v>
       </c>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2216,6 +3389,13 @@
       <c r="D111" s="3" t="n">
         <v>2999.25</v>
       </c>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2232,6 +3412,13 @@
       <c r="D112" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2248,6 +3435,13 @@
       <c r="D113" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2264,6 +3458,13 @@
       <c r="D114" s="3" t="n">
         <v>6299.5</v>
       </c>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2280,6 +3481,13 @@
       <c r="D115" s="3" t="n">
         <v>16248.75</v>
       </c>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2296,6 +3504,13 @@
       <c r="D116" s="3" t="n">
         <v>3649.5</v>
       </c>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2312,6 +3527,13 @@
       <c r="D117" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2328,6 +3550,13 @@
       <c r="D118" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2344,6 +3573,13 @@
       <c r="D119" s="3" t="n">
         <v>5249.25</v>
       </c>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2360,6 +3596,13 @@
       <c r="D120" s="3" t="n">
         <v>19998</v>
       </c>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2376,6 +3619,13 @@
       <c r="D121" s="3" t="n">
         <v>5999.25</v>
       </c>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2392,6 +3642,13 @@
       <c r="D122" s="3" t="n">
         <v>10798</v>
       </c>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2408,6 +3665,13 @@
       <c r="D123" s="3" t="n">
         <v>2749.75</v>
       </c>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2424,6 +3688,13 @@
       <c r="D124" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2440,6 +3711,13 @@
       <c r="D125" s="3" t="n">
         <v>1699.75</v>
       </c>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2456,6 +3734,13 @@
       <c r="D126" s="3" t="n">
         <v>1724.75</v>
       </c>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2472,6 +3757,13 @@
       <c r="D127" s="3" t="n">
         <v>8748.25</v>
       </c>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2488,6 +3780,13 @@
       <c r="D128" s="3" t="n">
         <v>2224.75</v>
       </c>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2504,6 +3803,13 @@
       <c r="D129" s="3" t="n">
         <v>2024.75</v>
       </c>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2520,6 +3826,17 @@
       <c r="D130" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E130" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2536,6 +3853,17 @@
       <c r="D131" s="3" t="n">
         <v>399.75</v>
       </c>
+      <c r="E131" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2552,6 +3880,13 @@
       <c r="D132" s="3" t="n">
         <v>2999.75</v>
       </c>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2568,6 +3903,13 @@
       <c r="D133" s="3" t="n">
         <v>16999</v>
       </c>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2584,6 +3926,13 @@
       <c r="D134" s="3" t="n">
         <v>4499.5</v>
       </c>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2600,6 +3949,13 @@
       <c r="D135" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2616,6 +3972,13 @@
       <c r="D136" s="3" t="n">
         <v>2998.75</v>
       </c>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2632,6 +3995,13 @@
       <c r="D137" s="3" t="n">
         <v>1049.5</v>
       </c>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2648,6 +4018,17 @@
       <c r="D138" s="3" t="n">
         <v>18749.25</v>
       </c>
+      <c r="E138" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2664,6 +4045,17 @@
       <c r="D139" s="3" t="n">
         <v>599.75</v>
       </c>
+      <c r="E139" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2680,6 +4072,17 @@
       <c r="D140" s="3" t="n">
         <v>6099</v>
       </c>
+      <c r="E140" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2696,6 +4099,17 @@
       <c r="D141" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E141" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2712,6 +4126,17 @@
       <c r="D142" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E142" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2728,6 +4153,17 @@
       <c r="D143" s="3" t="n">
         <v>7199</v>
       </c>
+      <c r="E143" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2744,6 +4180,17 @@
       <c r="D144" s="3" t="n">
         <v>4749.75</v>
       </c>
+      <c r="E144" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2760,6 +4207,17 @@
       <c r="D145" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E145" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2776,6 +4234,17 @@
       <c r="D146" s="3" t="n">
         <v>874.75</v>
       </c>
+      <c r="E146" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2792,13 +4261,19 @@
       <c r="D147" s="3" t="n">
         <v>924.75</v>
       </c>
+      <c r="E147" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «измельчитель» все бренды — 55 шт</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="B148" s="2" t="n">
         <v>1</v>
       </c>
@@ -2808,6 +4283,13 @@
       <c r="D148" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>в исходнике нет наименования</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2824,6 +4306,17 @@
       <c r="D149" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E149" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2840,6 +4333,17 @@
       <c r="D150" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E150" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2856,6 +4360,17 @@
       <c r="D151" s="3" t="n">
         <v>4899.5</v>
       </c>
+      <c r="E151" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2872,6 +4387,17 @@
       <c r="D152" s="3" t="n">
         <v>3749.75</v>
       </c>
+      <c r="E152" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2888,6 +4414,17 @@
       <c r="D153" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E153" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2904,6 +4441,13 @@
       <c r="D154" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2920,6 +4464,13 @@
       <c r="D155" s="3" t="n">
         <v>724.75</v>
       </c>
+      <c r="E155" s="4" t="n"/>
+      <c r="F155" s="4" t="n"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2936,6 +4487,13 @@
       <c r="D156" s="3" t="n">
         <v>1699.5</v>
       </c>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2952,6 +4510,17 @@
       <c r="D157" s="3" t="n">
         <v>3149.5</v>
       </c>
+      <c r="E157" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2968,6 +4537,17 @@
       <c r="D158" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E158" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2984,6 +4564,17 @@
       <c r="D159" s="3" t="n">
         <v>2749.75</v>
       </c>
+      <c r="E159" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3000,6 +4591,17 @@
       <c r="D160" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E160" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3016,6 +4618,17 @@
       <c r="D161" s="3" t="n">
         <v>4874.25</v>
       </c>
+      <c r="E161" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3032,6 +4645,17 @@
       <c r="D162" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E162" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3048,6 +4672,17 @@
       <c r="D163" s="3" t="n">
         <v>3749.25</v>
       </c>
+      <c r="E163" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3064,6 +4699,17 @@
       <c r="D164" s="3" t="n">
         <v>2999.75</v>
       </c>
+      <c r="E164" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3080,6 +4726,17 @@
       <c r="D165" s="3" t="n">
         <v>6749.25</v>
       </c>
+      <c r="E165" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3096,6 +4753,17 @@
       <c r="D166" s="3" t="n">
         <v>7873.25</v>
       </c>
+      <c r="E166" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3112,6 +4780,17 @@
       <c r="D167" s="3" t="n">
         <v>9998.75</v>
       </c>
+      <c r="E167" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3128,6 +4807,17 @@
       <c r="D168" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E168" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3144,6 +4834,17 @@
       <c r="D169" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E169" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3160,6 +4861,17 @@
       <c r="D170" s="3" t="n">
         <v>3699</v>
       </c>
+      <c r="E170" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3176,6 +4888,17 @@
       <c r="D171" s="3" t="n">
         <v>2374.75</v>
       </c>
+      <c r="E171" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3192,6 +4915,17 @@
       <c r="D172" s="3" t="n">
         <v>2099.75</v>
       </c>
+      <c r="E172" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3208,6 +4942,17 @@
       <c r="D173" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E173" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3224,6 +4969,17 @@
       <c r="D174" s="3" t="n">
         <v>3399.5</v>
       </c>
+      <c r="E174" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3240,6 +4996,17 @@
       <c r="D175" s="3" t="n">
         <v>3674.25</v>
       </c>
+      <c r="E175" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3256,6 +5023,17 @@
       <c r="D176" s="3" t="n">
         <v>107489.25</v>
       </c>
+      <c r="E176" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>116.96</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3272,6 +5050,17 @@
       <c r="D177" s="3" t="n">
         <v>19999</v>
       </c>
+      <c r="E177" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3288,6 +5077,17 @@
       <c r="D178" s="3" t="n">
         <v>15999.6</v>
       </c>
+      <c r="E178" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3304,6 +5104,17 @@
       <c r="D179" s="3" t="n">
         <v>43997.25</v>
       </c>
+      <c r="E179" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3320,6 +5131,17 @@
       <c r="D180" s="3" t="n">
         <v>4999</v>
       </c>
+      <c r="E180" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3336,6 +5158,17 @@
       <c r="D181" s="3" t="n">
         <v>5999.25</v>
       </c>
+      <c r="E181" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3352,6 +5185,17 @@
       <c r="D182" s="3" t="n">
         <v>19799.4</v>
       </c>
+      <c r="E182" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3368,6 +5212,17 @@
       <c r="D183" s="3" t="n">
         <v>28999</v>
       </c>
+      <c r="E183" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3384,6 +5239,17 @@
       <c r="D184" s="3" t="n">
         <v>4499.75</v>
       </c>
+      <c r="E184" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «парогенератор» все бренды — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3400,6 +5266,17 @@
       <c r="D185" s="3" t="n">
         <v>6499.5</v>
       </c>
+      <c r="E185" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3416,6 +5293,17 @@
       <c r="D186" s="3" t="n">
         <v>11998.5</v>
       </c>
+      <c r="E186" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3432,6 +5320,17 @@
       <c r="D187" s="3" t="n">
         <v>7999</v>
       </c>
+      <c r="E187" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3448,6 +5347,17 @@
       <c r="D188" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E188" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3464,6 +5374,17 @@
       <c r="D189" s="3" t="n">
         <v>2249.25</v>
       </c>
+      <c r="E189" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>3.342</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «увлажнитель» все бренды — 656 шт</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3480,6 +5401,17 @@
       <c r="D190" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E190" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3496,6 +5428,13 @@
       <c r="D191" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E191" s="4" t="n"/>
+      <c r="F191" s="4" t="n"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3512,6 +5451,13 @@
       <c r="D192" s="3" t="n">
         <v>3749.25</v>
       </c>
+      <c r="E192" s="4" t="n"/>
+      <c r="F192" s="4" t="n"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3528,6 +5474,17 @@
       <c r="D193" s="3" t="n">
         <v>13990</v>
       </c>
+      <c r="E193" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «весы» все бренды — 62 шт</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3544,6 +5501,17 @@
       <c r="D194" s="3" t="n">
         <v>20247.75</v>
       </c>
+      <c r="E194" s="4" t="n">
+        <v>1.772</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>15.948</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION COLORSENSE KG1330D б/у</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3560,6 +5528,17 @@
       <c r="D195" s="3" t="n">
         <v>1899.5</v>
       </c>
+      <c r="E195" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M157 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3576,6 +5555,17 @@
       <c r="D196" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E196" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-G200S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3592,6 +5582,17 @@
       <c r="D197" s="3" t="n">
         <v>999.5</v>
       </c>
+      <c r="E197" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M1721 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3608,6 +5609,17 @@
       <c r="D198" s="3" t="n">
         <v>29592</v>
       </c>
+      <c r="E198" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-G194 б/у (+2)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3624,6 +5636,17 @@
       <c r="D199" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E199" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED EVOLUTION RK-M110 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3640,6 +5663,17 @@
       <c r="D200" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M111D б/у (+2)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3656,6 +5690,17 @@
       <c r="D201" s="3" t="n">
         <v>4999</v>
       </c>
+      <c r="E201" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION COLORSENSE AM108D б/у</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3672,6 +5717,17 @@
       <c r="D202" s="3" t="n">
         <v>2999.25</v>
       </c>
+      <c r="E202" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F202" s="4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION AM101 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3688,6 +5744,17 @@
       <c r="D203" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E203" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F203" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-M216S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3704,6 +5771,17 @@
       <c r="D204" s="3" t="n">
         <v>10498.5</v>
       </c>
+      <c r="E204" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F204" s="4" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3720,6 +5798,17 @@
       <c r="D205" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E205" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3736,6 +5825,17 @@
       <c r="D206" s="3" t="n">
         <v>6248.75</v>
       </c>
+      <c r="E206" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F206" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3752,6 +5852,17 @@
       <c r="D207" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E207" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «тостер» все бренды — 493 шт</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3768,6 +5879,17 @@
       <c r="D208" s="3" t="n">
         <v>9998.75</v>
       </c>
+      <c r="E208" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F208" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3784,6 +5906,17 @@
       <c r="D209" s="3" t="n">
         <v>7999</v>
       </c>
+      <c r="E209" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F209" s="4" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3800,6 +5933,17 @@
       <c r="D210" s="3" t="n">
         <v>4599.8</v>
       </c>
+      <c r="E210" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F210" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3816,6 +5960,17 @@
       <c r="D211" s="3" t="n">
         <v>8999.5</v>
       </c>
+      <c r="E211" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F211" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3832,6 +5987,13 @@
       <c r="D212" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E212" s="4" t="n"/>
+      <c r="F212" s="4" t="n"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3848,6 +6010,13 @@
       <c r="D213" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3864,6 +6033,13 @@
       <c r="D214" s="3" t="n">
         <v>9749.25</v>
       </c>
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="4" t="n"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3880,6 +6056,17 @@
       <c r="D215" s="3" t="n">
         <v>9199.6</v>
       </c>
+      <c r="E215" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F215" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3896,6 +6083,17 @@
       <c r="D216" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E216" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F216" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3912,6 +6110,17 @@
       <c r="D217" s="3" t="n">
         <v>2499.5</v>
       </c>
+      <c r="E217" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F217" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3928,6 +6137,17 @@
       <c r="D218" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E218" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F218" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Электросушилка RED SOLUTION RFD-0122 б/у (+1)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3944,6 +6164,17 @@
       <c r="D219" s="3" t="n">
         <v>1999</v>
       </c>
+      <c r="E219" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F219" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-G185 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3960,6 +6191,17 @@
       <c r="D220" s="3" t="n">
         <v>649.75</v>
       </c>
+      <c r="E220" s="4" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="F220" s="4" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION RK-M158 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3976,6 +6218,13 @@
       <c r="D221" s="3" t="n">
         <v>4599.8</v>
       </c>
+      <c r="E221" s="4" t="n"/>
+      <c r="F221" s="4" t="n"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3992,6 +6241,17 @@
       <c r="D222" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E222" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F222" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4008,6 +6268,13 @@
       <c r="D223" s="3" t="n">
         <v>3374.75</v>
       </c>
+      <c r="E223" s="4" t="n"/>
+      <c r="F223" s="4" t="n"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4024,6 +6291,17 @@
       <c r="D224" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E224" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F224" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4040,6 +6318,17 @@
       <c r="D225" s="3" t="n">
         <v>699.75</v>
       </c>
+      <c r="E225" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F225" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4056,6 +6345,13 @@
       <c r="D226" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E226" s="4" t="n"/>
+      <c r="F226" s="4" t="n"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4072,6 +6368,17 @@
       <c r="D227" s="3" t="n">
         <v>6998.25</v>
       </c>
+      <c r="E227" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F227" s="4" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4088,6 +6395,17 @@
       <c r="D228" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E228" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F228" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4104,6 +6422,17 @@
       <c r="D229" s="3" t="n">
         <v>4999.5</v>
       </c>
+      <c r="E229" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F229" s="4" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4120,6 +6449,17 @@
       <c r="D230" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E230" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F230" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4136,6 +6476,17 @@
       <c r="D231" s="3" t="n">
         <v>2249.25</v>
       </c>
+      <c r="E231" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F231" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4152,6 +6503,17 @@
       <c r="D232" s="3" t="n">
         <v>8396.5</v>
       </c>
+      <c r="E232" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F232" s="4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4168,6 +6530,17 @@
       <c r="D233" s="3" t="n">
         <v>1799.5</v>
       </c>
+      <c r="E233" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F233" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4184,6 +6557,17 @@
       <c r="D234" s="3" t="n">
         <v>549.75</v>
       </c>
+      <c r="E234" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F234" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4200,6 +6584,17 @@
       <c r="D235" s="3" t="n">
         <v>4499.25</v>
       </c>
+      <c r="E235" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F235" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4216,6 +6611,17 @@
       <c r="D236" s="3" t="n">
         <v>5999.5</v>
       </c>
+      <c r="E236" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F236" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4232,6 +6638,17 @@
       <c r="D237" s="3" t="n">
         <v>3249.75</v>
       </c>
+      <c r="E237" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F237" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4248,6 +6665,17 @@
       <c r="D238" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E238" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F238" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4264,6 +6692,17 @@
       <c r="D239" s="3" t="n">
         <v>20469.75</v>
       </c>
+      <c r="E239" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F239" s="4" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4280,6 +6719,17 @@
       <c r="D240" s="3" t="n">
         <v>27999.2</v>
       </c>
+      <c r="E240" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F240" s="4" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4296,6 +6746,17 @@
       <c r="D241" s="3" t="n">
         <v>4349.5</v>
       </c>
+      <c r="E241" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F241" s="4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4312,6 +6773,17 @@
       <c r="D242" s="3" t="n">
         <v>7999.5</v>
       </c>
+      <c r="E242" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F242" s="4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4328,6 +6800,17 @@
       <c r="D243" s="3" t="n">
         <v>10399.6</v>
       </c>
+      <c r="E243" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F243" s="4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4344,6 +6827,17 @@
       <c r="D244" s="3" t="n">
         <v>6998.25</v>
       </c>
+      <c r="E244" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F244" s="4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION G121 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4360,6 +6854,17 @@
       <c r="D245" s="3" t="n">
         <v>1949.25</v>
       </c>
+      <c r="E245" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F245" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED COLORSENSE AM120D б/у (+1)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4376,6 +6881,13 @@
       <c r="D246" s="3" t="n">
         <v>3249.5</v>
       </c>
+      <c r="E246" s="4" t="n"/>
+      <c r="F246" s="4" t="n"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4392,6 +6904,17 @@
       <c r="D247" s="3" t="n">
         <v>2249.25</v>
       </c>
+      <c r="E247" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F247" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED SOLUTION SkyKettle RK-G200S б/у</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4408,6 +6931,17 @@
       <c r="D248" s="3" t="n">
         <v>999.5</v>
       </c>
+      <c r="E248" s="4" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="F248" s="4" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Чайник RED EVOLUTION RK-G20 б/у</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4424,6 +6958,17 @@
       <c r="D249" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E249" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F249" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4440,6 +6985,17 @@
       <c r="D250" s="3" t="n">
         <v>1499.25</v>
       </c>
+      <c r="E250" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F250" s="4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Midea — 6 шт</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4456,6 +7012,17 @@
       <c r="D251" s="3" t="n">
         <v>1499.5</v>
       </c>
+      <c r="E251" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F251" s="4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Электрочайник Midea MK-9093 черный/148 б/у (+1)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4472,6 +7039,17 @@
       <c r="D252" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E252" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F252" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>та же модель в 1С: Электрочайник Midea MK-8076/108 б/у (+1)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4488,6 +7066,17 @@
       <c r="D253" s="3" t="n">
         <v>999.5</v>
       </c>
+      <c r="E253" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F253" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Midea — 6 шт</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4504,6 +7093,17 @@
       <c r="D254" s="3" t="n">
         <v>899.75</v>
       </c>
+      <c r="E254" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F254" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» все бренды — 3051 шт</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4520,6 +7120,17 @@
       <c r="D255" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E255" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F255" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4536,6 +7147,13 @@
       <c r="D256" s="3" t="n">
         <v>747.5</v>
       </c>
+      <c r="E256" s="4" t="n"/>
+      <c r="F256" s="4" t="n"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4552,6 +7170,17 @@
       <c r="D257" s="3" t="n">
         <v>624.75</v>
       </c>
+      <c r="E257" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F257" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4568,6 +7197,17 @@
       <c r="D258" s="3" t="n">
         <v>1624.75</v>
       </c>
+      <c r="E258" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F258" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4584,6 +7224,17 @@
       <c r="D259" s="3" t="n">
         <v>899.75</v>
       </c>
+      <c r="E259" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F259" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «плита» все бренды — 173 шт</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4600,6 +7251,17 @@
       <c r="D260" s="3" t="n">
         <v>1749.5</v>
       </c>
+      <c r="E260" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F260" s="4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «плита» все бренды — 173 шт</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4616,6 +7278,17 @@
       <c r="D261" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E261" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F261" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «плита» все бренды — 173 шт</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4632,6 +7305,13 @@
       <c r="D262" s="3" t="n">
         <v>3999.75</v>
       </c>
+      <c r="E262" s="4" t="n"/>
+      <c r="F262" s="4" t="n"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4648,6 +7328,13 @@
       <c r="D263" s="3" t="n">
         <v>6598</v>
       </c>
+      <c r="E263" s="4" t="n"/>
+      <c r="F263" s="4" t="n"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4664,6 +7351,13 @@
       <c r="D264" s="3" t="n">
         <v>5398</v>
       </c>
+      <c r="E264" s="4" t="n"/>
+      <c r="F264" s="4" t="n"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4680,6 +7374,17 @@
       <c r="D265" s="3" t="n">
         <v>699.75</v>
       </c>
+      <c r="E265" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F265" s="4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «миксер» все бренды — 396 шт</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4696,6 +7401,17 @@
       <c r="D266" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E266" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F266" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4712,6 +7428,17 @@
       <c r="D267" s="3" t="n">
         <v>4499.75</v>
       </c>
+      <c r="E267" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F267" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4728,6 +7455,17 @@
       <c r="D268" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E268" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F268" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4744,6 +7482,13 @@
       <c r="D269" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E269" s="4" t="n"/>
+      <c r="F269" s="4" t="n"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4760,6 +7505,13 @@
       <c r="D270" s="3" t="n">
         <v>649.75</v>
       </c>
+      <c r="E270" s="4" t="n"/>
+      <c r="F270" s="4" t="n"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4776,6 +7528,17 @@
       <c r="D271" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E271" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F271" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -4792,6 +7555,17 @@
       <c r="D272" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E272" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F272" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -4808,6 +7582,17 @@
       <c r="D273" s="3" t="n">
         <v>499.75</v>
       </c>
+      <c r="E273" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F273" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» все бренды — 3051 шт</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -4824,6 +7609,17 @@
       <c r="D274" s="3" t="n">
         <v>949.75</v>
       </c>
+      <c r="E274" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F274" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «утюг» все бренды — 36 шт</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4840,6 +7636,17 @@
       <c r="D275" s="3" t="n">
         <v>47998.8</v>
       </c>
+      <c r="E275" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F275" s="4" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4856,6 +7663,17 @@
       <c r="D276" s="3" t="n">
         <v>39999.2</v>
       </c>
+      <c r="E276" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F276" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4872,6 +7690,17 @@
       <c r="D277" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E277" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F277" s="4" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -4888,6 +7717,17 @@
       <c r="D278" s="3" t="n">
         <v>2599.5</v>
       </c>
+      <c r="E278" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F278" s="4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос-робот» все бренды — 28 шт</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4904,6 +7744,17 @@
       <c r="D279" s="3" t="n">
         <v>11249.25</v>
       </c>
+      <c r="E279" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F279" s="4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4920,6 +7771,13 @@
       <c r="D280" s="3" t="n">
         <v>13999</v>
       </c>
+      <c r="E280" s="4" t="n"/>
+      <c r="F280" s="4" t="n"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4936,6 +7794,17 @@
       <c r="D281" s="3" t="n">
         <v>7999.6</v>
       </c>
+      <c r="E281" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F281" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4952,6 +7821,17 @@
       <c r="D282" s="3" t="n">
         <v>5749.75</v>
       </c>
+      <c r="E282" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F282" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4968,6 +7848,17 @@
       <c r="D283" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E283" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F283" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4984,6 +7875,17 @@
       <c r="D284" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E284" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F284" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5000,6 +7902,17 @@
       <c r="D285" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E285" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="F285" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «увлажнитель» все бренды — 656 шт</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5016,6 +7929,17 @@
       <c r="D286" s="3" t="n">
         <v>3499.75</v>
       </c>
+      <c r="E286" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F286" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5032,6 +7956,17 @@
       <c r="D287" s="3" t="n">
         <v>5249.25</v>
       </c>
+      <c r="E287" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F287" s="4" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5048,6 +7983,17 @@
       <c r="D288" s="3" t="n">
         <v>3624.75</v>
       </c>
+      <c r="E288" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F288" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5064,6 +8010,13 @@
       <c r="D289" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E289" s="4" t="n"/>
+      <c r="F289" s="4" t="n"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5080,6 +8033,17 @@
       <c r="D290" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E290" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F290" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5096,6 +8060,13 @@
       <c r="D291" s="3" t="n">
         <v>5399.25</v>
       </c>
+      <c r="E291" s="4" t="n"/>
+      <c r="F291" s="4" t="n"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5112,6 +8083,13 @@
       <c r="D292" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E292" s="4" t="n"/>
+      <c r="F292" s="4" t="n"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5128,6 +8106,17 @@
       <c r="D293" s="3" t="n">
         <v>9999</v>
       </c>
+      <c r="E293" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F293" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5144,6 +8133,17 @@
       <c r="D294" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E294" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F294" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5160,6 +8160,13 @@
       <c r="D295" s="3" t="n">
         <v>4499.75</v>
       </c>
+      <c r="E295" s="4" t="n"/>
+      <c r="F295" s="4" t="n"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5176,6 +8183,13 @@
       <c r="D296" s="3" t="n">
         <v>3374.75</v>
       </c>
+      <c r="E296" s="4" t="n"/>
+      <c r="F296" s="4" t="n"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5192,6 +8206,13 @@
       <c r="D297" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E297" s="4" t="n"/>
+      <c r="F297" s="4" t="n"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5208,6 +8229,17 @@
       <c r="D298" s="3" t="n">
         <v>7999.5</v>
       </c>
+      <c r="E298" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F298" s="4" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5224,6 +8256,17 @@
       <c r="D299" s="3" t="n">
         <v>1999.75</v>
       </c>
+      <c r="E299" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F299" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5240,6 +8283,17 @@
       <c r="D300" s="3" t="n">
         <v>2999</v>
       </c>
+      <c r="E300" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F300" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5256,6 +8310,17 @@
       <c r="D301" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E301" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F301" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5272,6 +8337,17 @@
       <c r="D302" s="3" t="n">
         <v>2249.75</v>
       </c>
+      <c r="E302" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F302" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5288,6 +8364,13 @@
       <c r="D303" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E303" s="4" t="n"/>
+      <c r="F303" s="4" t="n"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5304,6 +8387,17 @@
       <c r="D304" s="3" t="n">
         <v>3624.75</v>
       </c>
+      <c r="E304" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F304" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «гриль» все бренды — 566 шт</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5320,6 +8414,17 @@
       <c r="D305" s="3" t="n">
         <v>3999</v>
       </c>
+      <c r="E305" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F305" s="4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «блендер» все бренды — 215 шт</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5336,6 +8441,17 @@
       <c r="D306" s="3" t="n">
         <v>3499.75</v>
       </c>
+      <c r="E306" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F306" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «отпариватель» все бренды — 245 шт</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5352,6 +8468,13 @@
       <c r="D307" s="3" t="n">
         <v>3999.75</v>
       </c>
+      <c r="E307" s="4" t="n"/>
+      <c r="F307" s="4" t="n"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5368,6 +8491,13 @@
       <c r="D308" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E308" s="4" t="n"/>
+      <c r="F308" s="4" t="n"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5384,6 +8514,17 @@
       <c r="D309" s="3" t="n">
         <v>14399.6</v>
       </c>
+      <c r="E309" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F309" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5400,6 +8541,17 @@
       <c r="D310" s="3" t="n">
         <v>19999.2</v>
       </c>
+      <c r="E310" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F310" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5416,6 +8568,17 @@
       <c r="D311" s="3" t="n">
         <v>3999.75</v>
       </c>
+      <c r="E311" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F311" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5432,6 +8595,17 @@
       <c r="D312" s="3" t="n">
         <v>749.75</v>
       </c>
+      <c r="E312" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F312" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5448,6 +8622,17 @@
       <c r="D313" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E313" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F313" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5464,6 +8649,17 @@
       <c r="D314" s="3" t="n">
         <v>1999.5</v>
       </c>
+      <c r="E314" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F314" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5480,6 +8676,17 @@
       <c r="D315" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E315" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F315" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5496,6 +8703,17 @@
       <c r="D316" s="3" t="n">
         <v>4124.25</v>
       </c>
+      <c r="E316" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F316" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «чайник» Redmond/Red — 33 шт</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5512,6 +8730,17 @@
       <c r="D317" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E317" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="F317" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «увлажнитель» все бренды — 656 шт</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5528,6 +8757,17 @@
       <c r="D318" s="3" t="n">
         <v>38997</v>
       </c>
+      <c r="E318" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F318" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5544,6 +8784,17 @@
       <c r="D319" s="3" t="n">
         <v>3249.75</v>
       </c>
+      <c r="E319" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F319" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5560,6 +8811,17 @@
       <c r="D320" s="3" t="n">
         <v>3999.8</v>
       </c>
+      <c r="E320" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F320" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «мясорубка» все бренды — 83 шт</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5576,6 +8838,13 @@
       <c r="D321" s="3" t="n">
         <v>999.75</v>
       </c>
+      <c r="E321" s="4" t="n"/>
+      <c r="F321" s="4" t="n"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5592,6 +8861,17 @@
       <c r="D322" s="3" t="n">
         <v>26999.4</v>
       </c>
+      <c r="E322" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F322" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5608,6 +8888,17 @@
       <c r="D323" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E323" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F323" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «пылесос» все бренды — 323 шт</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5624,6 +8915,13 @@
       <c r="D324" s="3" t="n">
         <v>3749.75</v>
       </c>
+      <c r="E324" s="4" t="n"/>
+      <c r="F324" s="4" t="n"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5640,6 +8938,13 @@
       <c r="D325" s="3" t="n">
         <v>2999.75</v>
       </c>
+      <c r="E325" s="4" t="n"/>
+      <c r="F325" s="4" t="n"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5656,6 +8961,13 @@
       <c r="D326" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E326" s="4" t="n"/>
+      <c r="F326" s="4" t="n"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5672,6 +8984,17 @@
       <c r="D327" s="3" t="n">
         <v>7499.25</v>
       </c>
+      <c r="E327" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F327" s="4" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -5688,6 +9011,17 @@
       <c r="D328" s="3" t="n">
         <v>17999.4</v>
       </c>
+      <c r="E328" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F328" s="4" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -5704,6 +9038,17 @@
       <c r="D329" s="3" t="n">
         <v>6999.8</v>
       </c>
+      <c r="E329" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F329" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофеварка» все бренды — 271 шт</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -5720,6 +9065,17 @@
       <c r="D330" s="3" t="n">
         <v>3499.75</v>
       </c>
+      <c r="E330" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="F330" s="4" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «парогенератор» все бренды — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -5736,6 +9092,17 @@
       <c r="D331" s="3" t="n">
         <v>1249.75</v>
       </c>
+      <c r="E331" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F331" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «сушилка» Redmond/Red — 4 шт</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -5752,6 +9119,13 @@
       <c r="D332" s="3" t="n">
         <v>2499.75</v>
       </c>
+      <c r="E332" s="4" t="n"/>
+      <c r="F332" s="4" t="n"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>нет похожих в 1С</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -5768,6 +9142,17 @@
       <c r="D333" s="3" t="n">
         <v>4249.75</v>
       </c>
+      <c r="E333" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F333" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «соковыжималка» все бренды — 573 шт</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5784,6 +9169,17 @@
       <c r="D334" s="3" t="n">
         <v>2999.5</v>
       </c>
+      <c r="E334" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F334" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «термопот» все бренды — 157 шт</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -5800,6 +9196,17 @@
       <c r="D335" s="3" t="n">
         <v>1499.75</v>
       </c>
+      <c r="E335" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F335" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «термопот» все бренды — 157 шт</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -5816,6 +9223,17 @@
       <c r="D336" s="3" t="n">
         <v>3449.25</v>
       </c>
+      <c r="E336" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F336" s="4" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -5832,6 +9250,17 @@
       <c r="D337" s="3" t="n">
         <v>3999.8</v>
       </c>
+      <c r="E337" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F337" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «кофейная станция» все бренды — 15 шт</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -5848,25 +9277,42 @@
       <c r="D338" s="3" t="n">
         <v>2299.5</v>
       </c>
+      <c r="E338" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F338" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>медиана по похожим: «аэрогриль» все бренды — 99 шт</t>
+        </is>
+      </c>
     </row>
     <row r="339">
-      <c r="A339" s="4" t="inlineStr">
+      <c r="A339" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B339" s="5">
+      <c r="B339" s="6">
         <f>SUM(B2:B338)</f>
         <v/>
       </c>
-      <c r="C339" s="6" t="n"/>
-      <c r="D339" s="6">
+      <c r="C339" s="7" t="n"/>
+      <c r="D339" s="7">
         <f>SUM(D2:D338)</f>
         <v/>
       </c>
+      <c r="E339" s="8" t="n"/>
+      <c r="F339" s="8">
+        <f>SUM(F2:F338)</f>
+        <v/>
+      </c>
+      <c r="G339" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D338"/>
+  <autoFilter ref="A1:G338"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/converted/ceny-dlya-nakladnoy-ot-bah-30-10-26.xlsx
+++ b/public/converted/ceny-dlya-nakladnoy-ot-bah-30-10-26.xlsx
@@ -1709,11 +1709,15 @@
       <c r="D47" s="3" t="n">
         <v>2499.75</v>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
+      <c r="E47" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -1732,11 +1736,15 @@
       <c r="D48" s="3" t="n">
         <v>5999.25</v>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
+      <c r="E48" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -1755,11 +1763,15 @@
       <c r="D49" s="3" t="n">
         <v>15122.25</v>
       </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
+      <c r="E49" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>12.1</v>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -1940,11 +1952,15 @@
       <c r="D56" s="3" t="n">
         <v>449.75</v>
       </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
+      <c r="E56" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.61</v>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «стайлер» — 16 шт</t>
         </is>
       </c>
     </row>
@@ -1963,11 +1979,15 @@
       <c r="D57" s="3" t="n">
         <v>1949.25</v>
       </c>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
+      <c r="E57" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1.83</v>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «стайлер» — 16 шт</t>
         </is>
       </c>
     </row>
@@ -2094,11 +2114,15 @@
       <c r="D62" s="3" t="n">
         <v>9749.25</v>
       </c>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
+      <c r="E62" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>3.15</v>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мойки окон» — 8 шт</t>
         </is>
       </c>
     </row>
@@ -2117,11 +2141,15 @@
       <c r="D63" s="3" t="n">
         <v>2499.75</v>
       </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
+      <c r="E63" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мойки окон» — 8 шт</t>
         </is>
       </c>
     </row>
@@ -2707,11 +2735,15 @@
       <c r="D85" s="3" t="n">
         <v>524.75</v>
       </c>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="4" t="n"/>
+      <c r="E85" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.35</v>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «плойк» — 5 шт</t>
         </is>
       </c>
     </row>
@@ -3297,11 +3329,15 @@
       <c r="D107" s="3" t="n">
         <v>4874.25</v>
       </c>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
+      <c r="E107" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>4.98</v>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3320,11 +3356,15 @@
       <c r="D108" s="3" t="n">
         <v>2249.25</v>
       </c>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="n"/>
+      <c r="E108" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>4.98</v>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3343,11 +3383,15 @@
       <c r="D109" s="3" t="n">
         <v>874.75</v>
       </c>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="4" t="n"/>
+      <c r="E109" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>1.66</v>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3366,11 +3410,15 @@
       <c r="D110" s="3" t="n">
         <v>4499.25</v>
       </c>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
+      <c r="E110" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>4.98</v>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3389,11 +3437,15 @@
       <c r="D111" s="3" t="n">
         <v>2999.25</v>
       </c>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="n"/>
+      <c r="E111" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>4.98</v>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3412,11 +3464,15 @@
       <c r="D112" s="3" t="n">
         <v>1499.5</v>
       </c>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
+      <c r="E112" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>3.32</v>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -3435,11 +3491,15 @@
       <c r="D113" s="3" t="n">
         <v>7499.25</v>
       </c>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
+      <c r="E113" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3458,11 +3518,15 @@
       <c r="D114" s="3" t="n">
         <v>6299.5</v>
       </c>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="4" t="n"/>
+      <c r="E114" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3481,11 +3545,15 @@
       <c r="D115" s="3" t="n">
         <v>16248.75</v>
       </c>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="n"/>
+      <c r="E115" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3504,11 +3572,15 @@
       <c r="D116" s="3" t="n">
         <v>3649.5</v>
       </c>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
+      <c r="E116" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3527,11 +3599,15 @@
       <c r="D117" s="3" t="n">
         <v>2249.75</v>
       </c>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
+      <c r="E117" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3550,11 +3626,15 @@
       <c r="D118" s="3" t="n">
         <v>2999.5</v>
       </c>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
+      <c r="E118" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>4.53</v>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3653,15 @@
       <c r="D119" s="3" t="n">
         <v>5249.25</v>
       </c>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
+      <c r="E119" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>6.795</v>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3596,11 +3680,15 @@
       <c r="D120" s="3" t="n">
         <v>19998</v>
       </c>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
+      <c r="E120" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>18.12</v>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3619,11 +3707,15 @@
       <c r="D121" s="3" t="n">
         <v>5999.25</v>
       </c>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
+      <c r="E121" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>6.795</v>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3642,11 +3734,15 @@
       <c r="D122" s="3" t="n">
         <v>10798</v>
       </c>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
+      <c r="E122" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>18.12</v>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3665,11 +3761,15 @@
       <c r="D123" s="3" t="n">
         <v>2749.75</v>
       </c>
-      <c r="E123" s="4" t="n"/>
-      <c r="F123" s="4" t="n"/>
+      <c r="E123" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3688,11 +3788,15 @@
       <c r="D124" s="3" t="n">
         <v>1499.75</v>
       </c>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="4" t="n"/>
+      <c r="E124" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3711,11 +3815,15 @@
       <c r="D125" s="3" t="n">
         <v>1699.75</v>
       </c>
-      <c r="E125" s="4" t="n"/>
-      <c r="F125" s="4" t="n"/>
+      <c r="E125" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3734,11 +3842,15 @@
       <c r="D126" s="3" t="n">
         <v>1724.75</v>
       </c>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="n"/>
+      <c r="E126" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3757,11 +3869,15 @@
       <c r="D127" s="3" t="n">
         <v>8748.25</v>
       </c>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
+      <c r="E127" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>15.855</v>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3780,11 +3896,15 @@
       <c r="D128" s="3" t="n">
         <v>2224.75</v>
       </c>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="n"/>
+      <c r="E128" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3803,11 +3923,15 @@
       <c r="D129" s="3" t="n">
         <v>2024.75</v>
       </c>
-      <c r="E129" s="4" t="n"/>
-      <c r="F129" s="4" t="n"/>
+      <c r="E129" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -3880,11 +4004,15 @@
       <c r="D132" s="3" t="n">
         <v>2999.75</v>
       </c>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="n"/>
+      <c r="E132" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кухонная машина» — 1 шт</t>
         </is>
       </c>
     </row>
@@ -3903,11 +4031,15 @@
       <c r="D133" s="3" t="n">
         <v>16999</v>
       </c>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="4" t="n"/>
+      <c r="E133" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>12.8</v>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кухонная машина» — 1 шт</t>
         </is>
       </c>
     </row>
@@ -3926,11 +4058,15 @@
       <c r="D134" s="3" t="n">
         <v>4499.5</v>
       </c>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
+      <c r="E134" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>4.2</v>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кухонный комбайн» — 1 шт</t>
         </is>
       </c>
     </row>
@@ -3949,11 +4085,15 @@
       <c r="D135" s="3" t="n">
         <v>499.75</v>
       </c>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="4" t="n"/>
+      <c r="E135" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кофемолк» — 89 шт</t>
         </is>
       </c>
     </row>
@@ -3972,11 +4112,15 @@
       <c r="D136" s="3" t="n">
         <v>2998.75</v>
       </c>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
+      <c r="E136" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кофемолк» — 89 шт</t>
         </is>
       </c>
     </row>
@@ -3995,11 +4139,15 @@
       <c r="D137" s="3" t="n">
         <v>1049.5</v>
       </c>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
+      <c r="E137" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>2.6</v>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кофемолк» — 89 шт</t>
         </is>
       </c>
     </row>
@@ -4441,11 +4589,15 @@
       <c r="D154" s="3" t="n">
         <v>749.75</v>
       </c>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="n"/>
+      <c r="E154" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>0.37</v>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «выпрямит» — 41 шт</t>
         </is>
       </c>
     </row>
@@ -4464,11 +4616,15 @@
       <c r="D155" s="3" t="n">
         <v>724.75</v>
       </c>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="4" t="n"/>
+      <c r="E155" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>0.37</v>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «выпрямит» — 41 шт</t>
         </is>
       </c>
     </row>
@@ -4487,11 +4643,15 @@
       <c r="D156" s="3" t="n">
         <v>1699.5</v>
       </c>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="n"/>
+      <c r="E156" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>0.74</v>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «выпрямит» — 41 шт</t>
         </is>
       </c>
     </row>
@@ -5428,11 +5588,15 @@
       <c r="D191" s="3" t="n">
         <v>999.75</v>
       </c>
-      <c r="E191" s="4" t="n"/>
-      <c r="F191" s="4" t="n"/>
+      <c r="E191" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -5451,11 +5615,15 @@
       <c r="D192" s="3" t="n">
         <v>3749.25</v>
       </c>
-      <c r="E192" s="4" t="n"/>
-      <c r="F192" s="4" t="n"/>
+      <c r="E192" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -5987,11 +6155,15 @@
       <c r="D212" s="3" t="n">
         <v>749.75</v>
       </c>
-      <c r="E212" s="4" t="n"/>
-      <c r="F212" s="4" t="n"/>
+      <c r="E212" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F212" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -6010,11 +6182,15 @@
       <c r="D213" s="3" t="n">
         <v>999.75</v>
       </c>
-      <c r="E213" s="4" t="n"/>
-      <c r="F213" s="4" t="n"/>
+      <c r="E213" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F213" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -6033,11 +6209,15 @@
       <c r="D214" s="3" t="n">
         <v>9749.25</v>
       </c>
-      <c r="E214" s="4" t="n"/>
-      <c r="F214" s="4" t="n"/>
+      <c r="E214" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F214" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -6218,11 +6398,15 @@
       <c r="D221" s="3" t="n">
         <v>4599.8</v>
       </c>
-      <c r="E221" s="4" t="n"/>
-      <c r="F221" s="4" t="n"/>
+      <c r="E221" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F221" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вертикальный пылесос» — 171 шт</t>
         </is>
       </c>
     </row>
@@ -6268,11 +6452,15 @@
       <c r="D223" s="3" t="n">
         <v>3374.75</v>
       </c>
-      <c r="E223" s="4" t="n"/>
-      <c r="F223" s="4" t="n"/>
+      <c r="E223" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F223" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -6345,11 +6533,15 @@
       <c r="D226" s="3" t="n">
         <v>624.75</v>
       </c>
-      <c r="E226" s="4" t="n"/>
-      <c r="F226" s="4" t="n"/>
+      <c r="E226" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F226" s="4" t="n">
+        <v>0.37</v>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «выпрямит» — 41 шт</t>
         </is>
       </c>
     </row>
@@ -6881,11 +7073,15 @@
       <c r="D246" s="3" t="n">
         <v>3249.5</v>
       </c>
-      <c r="E246" s="4" t="n"/>
-      <c r="F246" s="4" t="n"/>
+      <c r="E246" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F246" s="4" t="n">
+        <v>4.53</v>
+      </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -7147,11 +7343,15 @@
       <c r="D256" s="3" t="n">
         <v>747.5</v>
       </c>
-      <c r="E256" s="4" t="n"/>
-      <c r="F256" s="4" t="n"/>
+      <c r="E256" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F256" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -7305,11 +7505,15 @@
       <c r="D262" s="3" t="n">
         <v>3999.75</v>
       </c>
-      <c r="E262" s="4" t="n"/>
-      <c r="F262" s="4" t="n"/>
+      <c r="E262" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F262" s="4" t="n">
+        <v>2.65</v>
+      </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «индукционная плита» — 32 шт</t>
         </is>
       </c>
     </row>
@@ -7328,11 +7532,15 @@
       <c r="D263" s="3" t="n">
         <v>6598</v>
       </c>
-      <c r="E263" s="4" t="n"/>
-      <c r="F263" s="4" t="n"/>
+      <c r="E263" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F263" s="4" t="n">
+        <v>2.65</v>
+      </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «индукционная плита» — 32 шт</t>
         </is>
       </c>
     </row>
@@ -7351,11 +7559,15 @@
       <c r="D264" s="3" t="n">
         <v>5398</v>
       </c>
-      <c r="E264" s="4" t="n"/>
-      <c r="F264" s="4" t="n"/>
+      <c r="E264" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F264" s="4" t="n">
+        <v>2.65</v>
+      </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «индукционная плита» — 32 шт</t>
         </is>
       </c>
     </row>
@@ -7482,11 +7694,15 @@
       <c r="D269" s="3" t="n">
         <v>1999.75</v>
       </c>
-      <c r="E269" s="4" t="n"/>
-      <c r="F269" s="4" t="n"/>
+      <c r="E269" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F269" s="4" t="n">
+        <v>7.5</v>
+      </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -7505,11 +7721,15 @@
       <c r="D270" s="3" t="n">
         <v>649.75</v>
       </c>
-      <c r="E270" s="4" t="n"/>
-      <c r="F270" s="4" t="n"/>
+      <c r="E270" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F270" s="4" t="n">
+        <v>0.37</v>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «выпрямит» — 41 шт</t>
         </is>
       </c>
     </row>
@@ -7771,11 +7991,15 @@
       <c r="D280" s="3" t="n">
         <v>13999</v>
       </c>
-      <c r="E280" s="4" t="n"/>
-      <c r="F280" s="4" t="n"/>
+      <c r="E280" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F280" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мини-печь/духовка» — 9 шт</t>
         </is>
       </c>
     </row>
@@ -8010,11 +8234,15 @@
       <c r="D289" s="3" t="n">
         <v>7499.25</v>
       </c>
-      <c r="E289" s="4" t="n"/>
-      <c r="F289" s="4" t="n"/>
+      <c r="E289" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F289" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8060,11 +8288,15 @@
       <c r="D291" s="3" t="n">
         <v>5399.25</v>
       </c>
-      <c r="E291" s="4" t="n"/>
-      <c r="F291" s="4" t="n"/>
+      <c r="E291" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F291" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -8083,11 +8315,15 @@
       <c r="D292" s="3" t="n">
         <v>1499.75</v>
       </c>
-      <c r="E292" s="4" t="n"/>
-      <c r="F292" s="4" t="n"/>
+      <c r="E292" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F292" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вакууматор» — 85 шт</t>
         </is>
       </c>
     </row>
@@ -8160,11 +8396,15 @@
       <c r="D295" s="3" t="n">
         <v>4499.75</v>
       </c>
-      <c r="E295" s="4" t="n"/>
-      <c r="F295" s="4" t="n"/>
+      <c r="E295" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F295" s="4" t="n">
+        <v>7.5</v>
+      </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «скоровар» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8183,11 +8423,15 @@
       <c r="D296" s="3" t="n">
         <v>3374.75</v>
       </c>
-      <c r="E296" s="4" t="n"/>
-      <c r="F296" s="4" t="n"/>
+      <c r="E296" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F296" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8206,11 +8450,15 @@
       <c r="D297" s="3" t="n">
         <v>1499.75</v>
       </c>
-      <c r="E297" s="4" t="n"/>
-      <c r="F297" s="4" t="n"/>
+      <c r="E297" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F297" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8364,11 +8612,15 @@
       <c r="D303" s="3" t="n">
         <v>999.75</v>
       </c>
-      <c r="E303" s="4" t="n"/>
-      <c r="F303" s="4" t="n"/>
+      <c r="E303" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F303" s="4" t="n">
+        <v>1.66</v>
+      </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -8468,11 +8720,15 @@
       <c r="D307" s="3" t="n">
         <v>3999.75</v>
       </c>
-      <c r="E307" s="4" t="n"/>
-      <c r="F307" s="4" t="n"/>
+      <c r="E307" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F307" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кухонный комбайн» — 1 шт</t>
         </is>
       </c>
     </row>
@@ -8491,11 +8747,15 @@
       <c r="D308" s="3" t="n">
         <v>2499.75</v>
       </c>
-      <c r="E308" s="4" t="n"/>
-      <c r="F308" s="4" t="n"/>
+      <c r="E308" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F308" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «кухонный комбайн» — 1 шт</t>
         </is>
       </c>
     </row>
@@ -8838,11 +9098,15 @@
       <c r="D321" s="3" t="n">
         <v>999.75</v>
       </c>
-      <c r="E321" s="4" t="n"/>
-      <c r="F321" s="4" t="n"/>
+      <c r="E321" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F321" s="4" t="n">
+        <v>1.66</v>
+      </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «вафельниц» — 151 шт</t>
         </is>
       </c>
     </row>
@@ -8915,11 +9179,15 @@
       <c r="D324" s="3" t="n">
         <v>3749.75</v>
       </c>
-      <c r="E324" s="4" t="n"/>
-      <c r="F324" s="4" t="n"/>
+      <c r="E324" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F324" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8938,11 +9206,15 @@
       <c r="D325" s="3" t="n">
         <v>2999.75</v>
       </c>
-      <c r="E325" s="4" t="n"/>
-      <c r="F325" s="4" t="n"/>
+      <c r="E325" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F325" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -8961,11 +9233,15 @@
       <c r="D326" s="3" t="n">
         <v>2499.75</v>
       </c>
-      <c r="E326" s="4" t="n"/>
-      <c r="F326" s="4" t="n"/>
+      <c r="E326" s="4" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="F326" s="4" t="n">
+        <v>2.265</v>
+      </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мультиварка» — 2 шт</t>
         </is>
       </c>
     </row>
@@ -9119,11 +9395,15 @@
       <c r="D332" s="3" t="n">
         <v>2499.75</v>
       </c>
-      <c r="E332" s="4" t="n"/>
-      <c r="F332" s="4" t="n"/>
+      <c r="E332" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F332" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>нет похожих в 1С</t>
+          <t>по ближайшему виду в 1С: «мойки окон» — 8 шт</t>
         </is>
       </c>
     </row>
